--- a/golden_set/protocol_annotations/P-24_annotation.xlsx
+++ b/golden_set/protocol_annotations/P-24_annotation.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +41,24 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +77,24 @@
         <bgColor rgb="00FFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -74,11 +108,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,9 +485,12 @@
   </sheetPr>
   <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>ANNOTATION INSTRUCTIONS</t>
         </is>
@@ -585,47 +627,47 @@
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>section_number</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>extracted_title</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>extracted_page</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>is_correct (Y/N)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>correct_title</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>correct_page</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -645,10 +687,18 @@
       <c r="C2" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="n"/>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 5 (offset from 8)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -664,10 +714,18 @@
       <c r="C3" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D3" s="3" t="n"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 5 (offset from 8)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -683,7 +741,11 @@
       <c r="C4" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="D4" s="3" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
@@ -702,7 +764,11 @@
       <c r="C5" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="D5" s="3" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
@@ -721,7 +787,11 @@
       <c r="C6" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="D6" s="3" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
@@ -740,10 +810,18 @@
       <c r="C7" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="D7" s="3" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 87 (offset from 91)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -759,7 +837,11 @@
       <c r="C8" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="D8" s="3" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
@@ -778,10 +860,18 @@
       <c r="C9" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="D9" s="3" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 88 (offset from 91)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -797,7 +887,11 @@
       <c r="C10" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="D10" s="3" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
@@ -816,10 +910,18 @@
       <c r="C11" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="D11" s="3" t="n"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 87 (offset from 91)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -835,7 +937,11 @@
       <c r="C12" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="D12" s="3" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="n"/>
@@ -854,7 +960,11 @@
       <c r="C13" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="3" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
@@ -873,7 +983,11 @@
       <c r="C14" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="D14" s="3" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
@@ -892,7 +1006,11 @@
       <c r="C15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="3" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
@@ -911,7 +1029,11 @@
       <c r="C16" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="3" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
@@ -930,7 +1052,11 @@
       <c r="C17" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D17" s="3" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
@@ -949,10 +1075,22 @@
       <c r="C18" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="D18" s="3" t="n"/>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Section on page 3, not 57</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -968,10 +1106,18 @@
       <c r="C19" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="D19" s="3" t="n"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 59 (offset from 55)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -987,10 +1133,18 @@
       <c r="C20" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="D20" s="3" t="n"/>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 59 (offset from 55)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1006,10 +1160,18 @@
       <c r="C21" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="D21" s="3" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 55 (offset from 56)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1025,10 +1187,18 @@
       <c r="C22" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="D22" s="3" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 60 (offset from 56)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1044,10 +1214,18 @@
       <c r="C23" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="D23" s="3" t="n"/>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 61 (offset from 57)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1063,10 +1241,18 @@
       <c r="C24" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="D24" s="3" t="n"/>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 61 (offset from 57)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1082,10 +1268,18 @@
       <c r="C25" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="D25" s="3" t="n"/>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 62 (offset from 58)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1101,10 +1295,18 @@
       <c r="C26" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="D26" s="3" t="n"/>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 62 (offset from 58)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1120,10 +1322,18 @@
       <c r="C27" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="D27" s="3" t="n"/>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 63 (offset from 59)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1139,10 +1349,18 @@
       <c r="C28" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 63 (offset from 59)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1158,10 +1376,18 @@
       <c r="C29" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="D29" s="3" t="n"/>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 63 (offset from 59)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1177,10 +1403,18 @@
       <c r="C30" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="D30" s="3" t="n"/>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 64 (offset from 60)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -1196,10 +1430,18 @@
       <c r="C31" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="D31" s="3" t="n"/>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 64 (offset from 60)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1215,10 +1457,18 @@
       <c r="C32" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="D32" s="3" t="n"/>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 87 (offset from 83)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1234,10 +1484,22 @@
       <c r="C33" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="D33" s="3" t="n"/>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Section on page 3, not 93</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1253,7 +1515,11 @@
       <c r="C34" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="D34" s="3" t="n"/>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="n"/>
@@ -1272,7 +1538,11 @@
       <c r="C35" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="D35" s="3" t="n"/>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
@@ -1291,7 +1561,11 @@
       <c r="C36" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="D36" s="3" t="n"/>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="n"/>
